--- a/exam_forms/012_mini_math_quiz--exam_forms.xlsx
+++ b/exam_forms/012_mini_math_quiz--exam_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,18 +510,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>first_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>First Page</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -533,18 +533,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>second_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Second Page</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>third_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Student ID</t>
+          <t>Third Page</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>fourth_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is 1 + 1?</t>
+          <t>Fourth Page</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>fifth_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Fifth Page</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -625,18 +625,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>sixth_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is 2 + 2?</t>
+          <t>Sixth Page</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -648,18 +648,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>seventh_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Seventh Page</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -671,18 +671,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>eighth_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is 3 + 3?</t>
+          <t>Eighth Page</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -694,18 +694,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>ninth_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Ninth Page</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -717,18 +717,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>tenth_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is 4 + 4?</t>
+          <t>Tenth Page</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -740,18 +740,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>answer_4</t>
+          <t>eleventh_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Eleventh Page</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -763,18 +763,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>twelfth_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is 5 + 5?</t>
+          <t>Twelfth Page</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -786,18 +786,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>answer_5</t>
+          <t>thirteenth_page</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Thirteenth Page</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -809,18 +809,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>fourteenth_page</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is 6 + 6?</t>
+          <t>Fourteenth Page</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -832,18 +832,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>answer_6</t>
+          <t>fifteenth_page</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Fifteenth Page</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -855,18 +855,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>sixteenth_page</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is 7 + 7?</t>
+          <t>Sixteenth Page</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -878,18 +878,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>answer_7</t>
+          <t>seventeenth_page</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Seventeenth Page</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -901,18 +901,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>eighteenth_page</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is 8 + 8?</t>
+          <t>Eighteenth Page</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -924,18 +924,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>answer_8</t>
+          <t>nineteenth_page</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Nineteenth Page</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -947,18 +947,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>twentieth_page</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is 9 + 9?</t>
+          <t>Twentieth Page</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -970,18 +970,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>answer_9</t>
+          <t>twenty_first_page</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Twenty-First Page</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -993,18 +993,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>twenty_second_page</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What is 10 + 10?</t>
+          <t>Twenty-Second Page</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1016,18 +1016,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>answer_10</t>
+          <t>twenty_third_page</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Twenty-Third Page</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1039,41 +1039,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>twenty_fourth_page</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is 11 + 11?</t>
+          <t>Twenty-Fourth Page</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>answer_11</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
